--- a/data/form_700/sonoma_2021.xlsx
+++ b/data/form_700/sonoma_2021.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/david/local_csci/csc131_project/data/form_700/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B55A29B1-44A9-FC4A-B1E3-DF400DF54011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDFF8A36-F06E-EC4B-A50A-FABB6D001795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="24220" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="29020" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Schedule A1" sheetId="2" r:id="rId1"/>
@@ -38,6 +38,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Disclose the name of the business entity.</t>
         </r>
@@ -51,6 +52,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Provide a general description of the business activity of the entity (for example, pharmaceuticals, computers, automobile manufacturing, or communications).</t>
         </r>
@@ -64,6 +66,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Select the highest fair market value of your investment during the reporting period. If you are filing a candidate or an assuming office statement, indicate the fair market value on the filing date or the date you took office, respectively.</t>
         </r>
@@ -77,6 +80,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Identify the nature of your investment (for example, stocks, warrants, options, or bonds).</t>
         </r>
@@ -90,6 +94,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>If you initially acquired or entirely disposed of this  interest during the reporting period, enter the date acquired or disposed.</t>
         </r>
@@ -113,6 +118,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Report any investments or interests in real property held by the business entity or trust identified in part 1 if your pro rata share of the interest held was $2,000 or more during the reporting period.</t>
         </r>
@@ -124,8 +130,9 @@
           <rPr>
             <b/>
             <sz val="10"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Disclose the name of the business entity or trust.</t>
         </r>
@@ -139,6 +146,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Disclose the address of the business entity or trust.</t>
         </r>
@@ -152,6 +160,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Provide a general description of the business activity of the entity (for example, pharmaceuticals, computers, automobile manufacturing, or communications).</t>
         </r>
@@ -165,6 +174,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Select the highest fair market value of your investment during the reporting period. If you are filing a candidate or an assuming office statement, indicate the fair market value on the filing date or the date you took office, respectively.</t>
         </r>
@@ -178,6 +188,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>If you initially acquired or entirely disposed of this  interest during the reporting period, enter the date acquired or disposed.</t>
         </r>
@@ -191,6 +202,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Identify the nature of your investment (for example, stocks, warrants, options, or bonds).</t>
         </r>
@@ -204,6 +216,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Disclose your job title or business position held with the entity, (for example, if you were a director, officer, partner, trustee, employee, or held any position of management).</t>
         </r>
@@ -217,6 +230,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Select your pro rata share of the gross income received by the business entity or trust. This amount includes your pro rata share of the gross income from the business entity or trust, as well as your community property interest in your spouse’s or registered domestic partner’s share. Gross income is the total amount of income before deducting expenses, losses, or taxes.</t>
         </r>
@@ -230,6 +244,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Disclose the name of each reportable source of income from which your pro rata share is $10,000 or more.  (See Schedule A-2 Instructions for more information.)
 Use semiclon to separate names.</t>
@@ -244,6 +259,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Report any investments held by the business entity or trust identified in part 1 if your pro rata share of the interest held was $2,000 or more during the reporting period.</t>
         </r>
@@ -257,6 +273,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>If real property, report the address or other precise location (for example, an assessor’s parcel number).</t>
         </r>
@@ -270,6 +287,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Select the highest fair market value of your real property or investment during the reporting period.  (Report the fair market value of the portion of your residence claimed as a tax deduction if you are utilizing your residence for business purposes.)</t>
         </r>
@@ -283,6 +301,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>If you initially acquired or entirely disposed of this  interest during the reporting period, enter the date acquired or disposed.</t>
         </r>
@@ -296,6 +315,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Select the nature of your interest.   If you select "Leasehold" you must also type the years remaining on the lease.</t>
         </r>
@@ -309,6 +329,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>If investment, report the Name of Business Entity.</t>
         </r>
@@ -322,6 +343,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>If investment, report the Description of Business Activity.</t>
         </r>
@@ -335,6 +357,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Report the address or other precise location (for example, an assessor’s parcel number) of the real property.</t>
         </r>
@@ -343,6 +366,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -357,6 +381,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Report the City or other precise location.</t>
         </r>
@@ -370,6 +395,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Select the nature of your interest.</t>
         </r>
@@ -383,6 +409,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>If you select "Leasehold" you must also type the years remaining on the lease.</t>
         </r>
@@ -406,6 +433,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Loans from a private lender that total $500 or more and are secured by real property may be reportable. Reportable loans may be disclosed on Schedule B or Schedule C. Loans from commercial lending institutions made in the lender’s regular course of business on terms available to members of the public without regard to your official status are not reportable.</t>
         </r>
@@ -414,6 +442,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -428,6 +457,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Report the address or other precise location (for example, an assessor’s parcel number) of the real property.</t>
         </r>
@@ -436,6 +466,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -450,6 +481,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Report the city of the real property.</t>
         </r>
@@ -463,6 +495,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Select the highest fair market value of your interest in the real property during the reporting period (regardless of what you owe on the property). If you are filing a candidate or an assuming office statement, indicate the fair market value on the filing date or the date you took office, respectively.</t>
         </r>
@@ -471,6 +504,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -485,6 +519,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>If you initially acquired or entirely disposed of this interest in real property during the reporting period, enter the date acquired or disposed.</t>
         </r>
@@ -498,6 +533,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Select the nature of your interest.   If you select "Leasehold" you must also type the years remaining on the lease.</t>
         </r>
@@ -511,6 +547,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Select your pro rata share of the gross rental income received.  Gross income is the total amount of income before deducting expenses, losses, or taxes.</t>
         </r>
@@ -524,6 +561,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>If you had a 10% or greater interest in real property and received rental income, list the name of the source(s) if your pro rata share of the gross income from any single tenant was $10,000 or more during the reporting period.  If you received a total of $10,000 or more from two or more tenants acting in concert (e.g., in most cases, this will apply to married couples), disclose the name of each tenant. Otherwise, leave this section blank.</t>
         </r>
@@ -532,6 +570,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -546,6 +585,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Provide the name of the lender.</t>
         </r>
@@ -554,6 +594,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -568,6 +609,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Provide the address of the lender.</t>
         </r>
@@ -576,6 +618,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -590,6 +633,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve"> Identify a guarantor, if applicable.</t>
         </r>
@@ -603,6 +647,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Describe the lender's business activity.</t>
         </r>
@@ -616,6 +661,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Disclose the interest rate.  For variable interest rate loans, disclose the conditions of the loan (for example, Prime + 2) or the average interest rate paid during the reporting period.</t>
         </r>
@@ -624,6 +670,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -638,6 +685,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Disclose the term of the loan. The term of a loan is the total number of months or years given for repayment of the loan at the time the loan was established. </t>
         </r>
@@ -651,6 +699,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Select the highest balance of the loan during the reporting period.</t>
         </r>
@@ -659,6 +708,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -673,6 +723,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Select the nature of your interest.</t>
         </r>
@@ -686,6 +737,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>If you select "Leasehold" you must also type the years remaining on the lease.</t>
         </r>
@@ -709,6 +761,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>For income from rental property that is not required to be listed on Schedule B, enter “Rental Income” under “Name of Source,” check the box indicating the gross income received, and, if you had a 10% or greater interest in the rental property, list the name of each tenant if your pro rata share of the gross income from that tenant was $10,000 or more during the reporting period.</t>
         </r>
@@ -722,6 +775,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Disclose the name of each source of income or each business entity with which you held a business position.</t>
         </r>
@@ -735,6 +789,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Disclose the address of each source of income or each business entity with which you held a business position.</t>
         </r>
@@ -748,6 +803,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Provide a general description of the business activity if the source is a business entity (for example, pharmaceuticals, computers, automobile manufacturing, or communications).</t>
         </r>
@@ -761,6 +817,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Disclose your job title or business position held with the entity, (for example, if you were a director, officer, partner, trustee, employee, or held any position of management).</t>
         </r>
@@ -769,6 +826,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -783,6 +841,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Select the amount of gross income received.</t>
         </r>
@@ -796,6 +855,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Select the consideration for which the income was received. If you received commission or rental property income of $10,000 or more from a single source, you must provide the name of the source.</t>
         </r>
@@ -809,6 +869,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Select the consideration for which the income was received.</t>
         </r>
@@ -822,6 +883,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>If Sale of specify (Real property, car, boat, etc.)</t>
         </r>
@@ -835,6 +897,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>If you received commission or rental property income of $10,000 or more from a single source, you must provide the name of the source.</t>
         </r>
@@ -843,6 +906,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -868,6 +932,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Disclose the full name (not an acronym) of the source of the gift.</t>
         </r>
@@ -881,6 +946,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Disclose the address of the source of the gift.</t>
         </r>
@@ -894,6 +960,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Provide a general description of the business activity of the source (for example, pharmaceuticals, computers, automobile manufacturing, or communications).</t>
         </r>
@@ -907,6 +974,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Provide the entire date (month, day, and year) that the gift was received.</t>
         </r>
@@ -920,6 +988,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Provide the fair market value of the gift.</t>
         </r>
@@ -933,6 +1002,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Provide a description of the gift.</t>
         </r>
@@ -958,6 +1028,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Disclose the full name (not an acronym) of the source of the travel payment.</t>
         </r>
@@ -971,6 +1042,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Disclose the address of the source of the travel payment.</t>
         </r>
@@ -984,6 +1056,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Disclose the city and state of the source of the travel payment.</t>
         </r>
@@ -997,6 +1070,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Enter "Y" if this payment is from a 501(c)(3) organization</t>
         </r>
@@ -1010,6 +1084,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Provide a general description of the business activity of the source (for example, pharmaceuticals, computers, automobile manufacturing, or communications).</t>
         </r>
@@ -1023,6 +1098,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Disclose the entire date or range of dates, if gift.</t>
         </r>
@@ -1036,6 +1112,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Disclose the amount of income or the fair market value of the gift.</t>
         </r>
@@ -1044,6 +1121,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -1058,6 +1136,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Select either "gift" or "income" to indicate whether the payment was a gift or income.  Travel payments are gifts if you did not provide services that were equal to or greater in value than the payments received.  Travel payments are income if you provided services that were equal to or greater in value than the payments received.</t>
         </r>
@@ -1071,6 +1150,7 @@
             <sz val="10"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Provide a description of the travel payment.</t>
         </r>
@@ -1084,7 +1164,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Provide travel destination if gift.</t>
         </r>
@@ -1095,7 +1175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="395">
   <si>
     <t>Last Name</t>
   </si>
@@ -1147,6 +1227,7 @@
         <i/>
         <sz val="8"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>(Select from drop down list)</t>
     </r>
@@ -1162,6 +1243,7 @@
         <i/>
         <sz val="8"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>(Select from drop down list. 
 If "other," describe)</t>
@@ -1415,9 +1497,6 @@
     <t>Food Manufacturer</t>
   </si>
   <si>
-    <t>IBM</t>
-  </si>
-  <si>
     <t>Financial Institution</t>
   </si>
   <si>
@@ -1434,9 +1513,6 @@
   </si>
   <si>
     <t>Skyworks</t>
-  </si>
-  <si>
-    <t>Walmart</t>
   </si>
   <si>
     <t>Retail</t>
@@ -1475,6 +1551,7 @@
         <i/>
         <sz val="8"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>(For reporting a trust, enter the name and address then skip to box 2.)</t>
     </r>
@@ -1495,6 +1572,7 @@
         <i/>
         <sz val="8"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>(Use a separate line for each investment or real property interest.)</t>
     </r>
@@ -1514,6 +1592,7 @@
         <sz val="8"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">(Business Address Acceptable) </t>
     </r>
@@ -1523,6 +1602,7 @@
         <sz val="8"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -1534,6 +1614,7 @@
         <sz val="8"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>(If Trust, go to 2)</t>
     </r>
@@ -1555,6 +1636,7 @@
         <i/>
         <sz val="8"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>(if "other," describe)</t>
     </r>
@@ -1600,6 +1682,7 @@
         <i/>
         <sz val="8"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>(if "other," describe)</t>
     </r>
@@ -1808,6 +1891,7 @@
         <sz val="8"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 
 </t>
@@ -1818,6 +1902,7 @@
         <sz val="7"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">(Business Address Acceptable) </t>
     </r>
@@ -1992,6 +2077,7 @@
       <rPr>
         <sz val="8"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>(if "other," describe)</t>
     </r>
@@ -2006,6 +2092,7 @@
         <sz val="7"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>(Real property, car, boat, etc.)</t>
     </r>
@@ -2020,6 +2107,7 @@
         <sz val="7"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>(Comission or Rental Income)</t>
     </r>
@@ -2300,6 +2388,7 @@
         <i/>
         <sz val="8"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>(Business Address Acceptable)</t>
     </r>
@@ -2378,97 +2467,106 @@
     <t>Stryker</t>
   </si>
   <si>
+    <t>MFGP#Micro Focus International</t>
+  </si>
+  <si>
+    <t>PRSP#Perspecta</t>
+  </si>
+  <si>
+    <t>Caterpiller</t>
+  </si>
+  <si>
+    <t>Cisco</t>
+  </si>
+  <si>
+    <t>FedEx</t>
+  </si>
+  <si>
+    <t>Ford Motor</t>
+  </si>
+  <si>
+    <t>General Motors#GMC</t>
+  </si>
+  <si>
+    <t>Alibaba Group Holding</t>
+  </si>
+  <si>
+    <t>UBS Financial Services</t>
+  </si>
+  <si>
+    <t>Reed Gilliland</t>
+  </si>
+  <si>
+    <t>Altria Group</t>
+  </si>
+  <si>
+    <t>Apple#AAPL</t>
+  </si>
+  <si>
+    <t>Berkshire Hathaway</t>
+  </si>
+  <si>
+    <t>Microsoft#MSFT</t>
+  </si>
+  <si>
+    <t>Mondelez Intl#Mondelez International</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank of America </t>
+  </si>
+  <si>
+    <t>Canopy Growth</t>
+  </si>
+  <si>
+    <t>Gore Country</t>
+  </si>
+  <si>
+    <t>North Bay Strategies</t>
+  </si>
+  <si>
+    <t>E&amp;M#Electric and Machinery</t>
+  </si>
+  <si>
+    <t>Deas Family</t>
+  </si>
+  <si>
+    <t>CA Alfred E. Alquist Seismic Safety Commission#Seismic Safety Commission#Alfred E. Alquist</t>
+  </si>
+  <si>
+    <t>Golden Gate Bridge Highway Transportation</t>
+  </si>
+  <si>
+    <t>Metropolitan Transportation</t>
+  </si>
+  <si>
+    <t>Untitled Labs</t>
+  </si>
+  <si>
+    <t>Howroyd Wright Employment Agency</t>
+  </si>
+  <si>
+    <t>HPE#Hewlett-Packard Enterprises#Hewlett Packard Enterprises</t>
+  </si>
+  <si>
+    <t>DXC#DXC Technology</t>
+  </si>
+  <si>
+    <t>JP Morgan Chase#JP Morgan</t>
+  </si>
+  <si>
+    <t>IBM#International Business Machines</t>
+  </si>
+  <si>
+    <t>Walmart#WMT</t>
+  </si>
+  <si>
     <t>Walt Disney</t>
   </si>
   <si>
-    <t>MFGP#Micro Focus International</t>
-  </si>
-  <si>
-    <t>HPE#Hewlett Packard Enterprises</t>
-  </si>
-  <si>
-    <t>PRSP#Perspecta</t>
-  </si>
-  <si>
-    <t>DXC</t>
-  </si>
-  <si>
-    <t>HPQ#HP#Hewlett Packard</t>
-  </si>
-  <si>
-    <t>Caterpiller</t>
-  </si>
-  <si>
-    <t>Cisco</t>
-  </si>
-  <si>
-    <t>FedEx</t>
-  </si>
-  <si>
-    <t>Ford Motor</t>
-  </si>
-  <si>
-    <t>General Motors#GMC</t>
-  </si>
-  <si>
-    <t>Alibaba Group Holding</t>
-  </si>
-  <si>
-    <t>UBS Financial Services</t>
-  </si>
-  <si>
-    <t>Reed Gilliland</t>
-  </si>
-  <si>
-    <t>Altria Group</t>
-  </si>
-  <si>
-    <t>Apple#AAPL</t>
-  </si>
-  <si>
-    <t>Berkshire Hathaway</t>
-  </si>
-  <si>
-    <t>JP Morgan Chase</t>
-  </si>
-  <si>
-    <t>Microsoft#MSFT</t>
-  </si>
-  <si>
-    <t>Mondelez Intl#Mondelez International</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bank of America </t>
-  </si>
-  <si>
-    <t>Canopy Growth</t>
-  </si>
-  <si>
-    <t>Gore Country</t>
-  </si>
-  <si>
-    <t>North Bay Strategies</t>
-  </si>
-  <si>
-    <t>E&amp;M#Electric and Machinery</t>
-  </si>
-  <si>
-    <t>Deas Family</t>
-  </si>
-  <si>
-    <t>CA Alfred E. Alquist Seismic Safety Commission#Seismic Safety Commission#Alfred E. Alquist</t>
-  </si>
-  <si>
-    <t>Golden Gate Bridge Highway Transportation</t>
-  </si>
-  <si>
-    <t>Metropolitan Transportation</t>
-  </si>
-  <si>
-    <t>Untitled Labs</t>
-  </si>
-  <si>
-    <t>Howroyd Wright Employment Agency</t>
+    <t>HPQ#Hewlett-Packard#Hewlett Packard</t>
+  </si>
+  <si>
+    <t>landpaths</t>
   </si>
 </sst>
 </file>
@@ -2489,21 +2587,25 @@
       <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <i/>
       <sz val="8"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -2511,28 +2613,33 @@
       <sz val="8"/>
       <color indexed="8"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="8"/>
       <color indexed="8"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <color indexed="8"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="7"/>
       <color indexed="8"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="7"/>
       <color indexed="8"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -2545,28 +2652,31 @@
       <sz val="10"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -2583,7 +2693,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -2645,11 +2755,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2673,11 +2794,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2989,7 +3111,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:Q52"/>
+  <dimension ref="A1:Q53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
@@ -3011,72 +3133,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="N1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="O1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="11" t="s">
+      <c r="P1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="11"/>
+      <c r="Q1" s="13"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
       <c r="P2" s="1" t="s">
         <v>16</v>
       </c>
@@ -3114,8 +3236,8 @@
       <c r="K3" s="3">
         <v>44620.73710648148</v>
       </c>
-      <c r="L3" s="12" t="s">
-        <v>356</v>
+      <c r="L3" s="11" t="s">
+        <v>354</v>
       </c>
       <c r="M3" s="4" t="s">
         <v>25</v>
@@ -3159,8 +3281,8 @@
       <c r="K4" s="6">
         <v>44620.73710648148</v>
       </c>
-      <c r="L4" s="13" t="s">
-        <v>357</v>
+      <c r="L4" s="12" t="s">
+        <v>355</v>
       </c>
       <c r="M4" s="7" t="s">
         <v>25</v>
@@ -3204,8 +3326,8 @@
       <c r="K5" s="6">
         <v>44620.73710648148</v>
       </c>
-      <c r="L5" s="13" t="s">
-        <v>358</v>
+      <c r="L5" s="12" t="s">
+        <v>356</v>
       </c>
       <c r="M5" s="7" t="s">
         <v>25</v>
@@ -3249,8 +3371,8 @@
       <c r="K6" s="6">
         <v>44620.73710648148</v>
       </c>
-      <c r="L6" s="13" t="s">
-        <v>368</v>
+      <c r="L6" s="7" t="s">
+        <v>393</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>27</v>
@@ -3294,8 +3416,8 @@
       <c r="K7" s="6">
         <v>44620.73710648148</v>
       </c>
-      <c r="L7" s="13" t="s">
-        <v>359</v>
+      <c r="L7" s="12" t="s">
+        <v>357</v>
       </c>
       <c r="M7" s="7" t="s">
         <v>25</v>
@@ -3339,8 +3461,8 @@
       <c r="K8" s="6">
         <v>44620.73710648148</v>
       </c>
-      <c r="L8" s="13" t="s">
-        <v>353</v>
+      <c r="L8" s="12" t="s">
+        <v>351</v>
       </c>
       <c r="M8" s="7" t="s">
         <v>30</v>
@@ -3384,8 +3506,8 @@
       <c r="K9" s="6">
         <v>44620.73710648148</v>
       </c>
-      <c r="L9" s="13" t="s">
-        <v>360</v>
+      <c r="L9" s="12" t="s">
+        <v>358</v>
       </c>
       <c r="M9" s="7" t="s">
         <v>25</v>
@@ -3429,8 +3551,8 @@
       <c r="K10" s="6">
         <v>44620.73710648148</v>
       </c>
-      <c r="L10" s="13" t="s">
-        <v>361</v>
+      <c r="L10" s="12" t="s">
+        <v>359</v>
       </c>
       <c r="M10" s="7" t="s">
         <v>31</v>
@@ -3474,8 +3596,8 @@
       <c r="K11" s="6">
         <v>44620.73710648148</v>
       </c>
-      <c r="L11" s="13" t="s">
-        <v>362</v>
+      <c r="L11" s="12" t="s">
+        <v>360</v>
       </c>
       <c r="M11" s="7" t="s">
         <v>30</v>
@@ -3519,8 +3641,8 @@
       <c r="K12" s="6">
         <v>44635.468206018515</v>
       </c>
-      <c r="L12" s="13" t="s">
-        <v>363</v>
+      <c r="L12" s="7" t="s">
+        <v>392</v>
       </c>
       <c r="M12" s="7" t="s">
         <v>37</v>
@@ -3566,7 +3688,7 @@
       <c r="K13" s="6">
         <v>44783.347083912035</v>
       </c>
-      <c r="L13" s="13" t="s">
+      <c r="L13" s="12" t="s">
         <v>43</v>
       </c>
       <c r="M13" s="7" t="s">
@@ -3613,8 +3735,8 @@
       <c r="K14" s="6">
         <v>44783.347083912035</v>
       </c>
-      <c r="L14" s="13" t="s">
-        <v>354</v>
+      <c r="L14" s="12" t="s">
+        <v>352</v>
       </c>
       <c r="M14" s="7" t="s">
         <v>46</v>
@@ -3707,8 +3829,8 @@
       <c r="K16" s="6">
         <v>44628.593032407407</v>
       </c>
-      <c r="L16" s="13" t="s">
-        <v>355</v>
+      <c r="L16" s="12" t="s">
+        <v>353</v>
       </c>
       <c r="M16" s="7" t="s">
         <v>52</v>
@@ -3754,8 +3876,8 @@
       <c r="K17" s="6">
         <v>44628.593032407407</v>
       </c>
-      <c r="L17" s="13" t="s">
-        <v>364</v>
+      <c r="L17" s="12" t="s">
+        <v>361</v>
       </c>
       <c r="M17" s="7" t="s">
         <v>52</v>
@@ -3801,8 +3923,8 @@
       <c r="K18" s="6">
         <v>44628.593032407407</v>
       </c>
-      <c r="L18" s="13" t="s">
-        <v>365</v>
+      <c r="L18" s="7" t="s">
+        <v>387</v>
       </c>
       <c r="M18" s="7" t="s">
         <v>52</v>
@@ -3848,8 +3970,8 @@
       <c r="K19" s="6">
         <v>44628.593032407407</v>
       </c>
-      <c r="L19" s="13" t="s">
-        <v>366</v>
+      <c r="L19" s="12" t="s">
+        <v>362</v>
       </c>
       <c r="M19" s="7" t="s">
         <v>52</v>
@@ -3895,8 +4017,8 @@
       <c r="K20" s="6">
         <v>44628.593032407407</v>
       </c>
-      <c r="L20" s="13" t="s">
-        <v>367</v>
+      <c r="L20" s="7" t="s">
+        <v>388</v>
       </c>
       <c r="M20" s="7" t="s">
         <v>52</v>
@@ -3942,8 +4064,8 @@
       <c r="K21" s="6">
         <v>44628.593032407407</v>
       </c>
-      <c r="L21" s="13" t="s">
-        <v>368</v>
+      <c r="L21" s="7" t="s">
+        <v>393</v>
       </c>
       <c r="M21" s="7" t="s">
         <v>52</v>
@@ -3987,8 +4109,8 @@
       <c r="K22" s="6">
         <v>44615.621944444443</v>
       </c>
-      <c r="L22" s="13" t="s">
-        <v>369</v>
+      <c r="L22" s="12" t="s">
+        <v>363</v>
       </c>
       <c r="M22" s="7" t="s">
         <v>57</v>
@@ -4032,8 +4154,8 @@
       <c r="K23" s="6">
         <v>44615.621944444443</v>
       </c>
-      <c r="L23" s="13" t="s">
-        <v>370</v>
+      <c r="L23" s="12" t="s">
+        <v>364</v>
       </c>
       <c r="M23" s="7" t="s">
         <v>58</v>
@@ -4122,8 +4244,8 @@
       <c r="K25" s="6">
         <v>44615.621944444443</v>
       </c>
-      <c r="L25" s="13" t="s">
-        <v>371</v>
+      <c r="L25" s="12" t="s">
+        <v>365</v>
       </c>
       <c r="M25" s="7" t="s">
         <v>61</v>
@@ -4167,8 +4289,8 @@
       <c r="K26" s="6">
         <v>44615.621944444443</v>
       </c>
-      <c r="L26" s="13" t="s">
-        <v>372</v>
+      <c r="L26" s="12" t="s">
+        <v>366</v>
       </c>
       <c r="M26" s="7" t="s">
         <v>62</v>
@@ -4212,8 +4334,8 @@
       <c r="K27" s="6">
         <v>44615.621944444443</v>
       </c>
-      <c r="L27" s="13" t="s">
-        <v>373</v>
+      <c r="L27" s="12" t="s">
+        <v>367</v>
       </c>
       <c r="M27" s="7" t="s">
         <v>62</v>
@@ -4353,8 +4475,8 @@
       <c r="K30" s="6">
         <v>44587.558275462958</v>
       </c>
-      <c r="L30" s="13" t="s">
-        <v>374</v>
+      <c r="L30" s="12" t="s">
+        <v>368</v>
       </c>
       <c r="M30" s="7" t="s">
         <v>75</v>
@@ -4400,8 +4522,8 @@
       <c r="K31" s="6">
         <v>44587.558275462958</v>
       </c>
-      <c r="L31" s="13" t="s">
-        <v>375</v>
+      <c r="L31" s="12" t="s">
+        <v>369</v>
       </c>
       <c r="M31" s="7" t="s">
         <v>76</v>
@@ -4445,8 +4567,8 @@
       <c r="K32" s="6">
         <v>44572.604270833333</v>
       </c>
-      <c r="L32" s="13" t="s">
-        <v>376</v>
+      <c r="L32" s="12" t="s">
+        <v>370</v>
       </c>
       <c r="M32" s="7" t="s">
         <v>82</v>
@@ -4490,8 +4612,8 @@
       <c r="K33" s="6">
         <v>44631.713113425925</v>
       </c>
-      <c r="L33" s="13" t="s">
-        <v>377</v>
+      <c r="L33" s="12" t="s">
+        <v>371</v>
       </c>
       <c r="M33" s="7" t="s">
         <v>88</v>
@@ -4535,8 +4657,8 @@
       <c r="K34" s="6">
         <v>44631.713113425925</v>
       </c>
-      <c r="L34" s="13" t="s">
-        <v>378</v>
+      <c r="L34" s="12" t="s">
+        <v>372</v>
       </c>
       <c r="M34" s="7" t="s">
         <v>44</v>
@@ -4580,8 +4702,8 @@
       <c r="K35" s="6">
         <v>44631.713113425925</v>
       </c>
-      <c r="L35" s="13" t="s">
-        <v>379</v>
+      <c r="L35" s="12" t="s">
+        <v>373</v>
       </c>
       <c r="M35" s="7" t="s">
         <v>89</v>
@@ -4806,7 +4928,7 @@
         <v>44631.713113425925</v>
       </c>
       <c r="L40" s="7" t="s">
-        <v>97</v>
+        <v>390</v>
       </c>
       <c r="M40" s="7" t="s">
         <v>44</v>
@@ -4850,11 +4972,11 @@
       <c r="K41" s="6">
         <v>44631.713113425925</v>
       </c>
-      <c r="L41" s="13" t="s">
-        <v>380</v>
+      <c r="L41" s="7" t="s">
+        <v>389</v>
       </c>
       <c r="M41" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="N41" s="7" t="s">
         <v>28</v>
@@ -4896,7 +5018,7 @@
         <v>44631.713113425925</v>
       </c>
       <c r="L42" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M42" s="7" t="s">
         <v>44</v>
@@ -4940,8 +5062,8 @@
       <c r="K43" s="6">
         <v>44631.713113425925</v>
       </c>
-      <c r="L43" s="13" t="s">
-        <v>381</v>
+      <c r="L43" s="12" t="s">
+        <v>374</v>
       </c>
       <c r="M43" s="7" t="s">
         <v>44</v>
@@ -4985,11 +5107,11 @@
       <c r="K44" s="6">
         <v>44631.713113425925</v>
       </c>
-      <c r="L44" s="13" t="s">
-        <v>382</v>
+      <c r="L44" s="12" t="s">
+        <v>375</v>
       </c>
       <c r="M44" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N44" s="7" t="s">
         <v>28</v>
@@ -5031,10 +5153,10 @@
         <v>44631.713113425925</v>
       </c>
       <c r="L45" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="M45" s="7" t="s">
         <v>101</v>
-      </c>
-      <c r="M45" s="7" t="s">
-        <v>102</v>
       </c>
       <c r="N45" s="7" t="s">
         <v>28</v>
@@ -5076,7 +5198,7 @@
         <v>44631.713113425925</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M46" s="7" t="s">
         <v>44</v>
@@ -5120,11 +5242,11 @@
       <c r="K47" s="6">
         <v>44631.713113425925</v>
       </c>
-      <c r="L47" s="13" t="s">
-        <v>104</v>
+      <c r="L47" s="7" t="s">
+        <v>391</v>
       </c>
       <c r="M47" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N47" s="7" t="s">
         <v>28</v>
@@ -5165,11 +5287,11 @@
       <c r="K48" s="6">
         <v>44631.713113425925</v>
       </c>
-      <c r="L48" s="13" t="s">
-        <v>383</v>
+      <c r="L48" s="12" t="s">
+        <v>376</v>
       </c>
       <c r="M48" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="N48" s="7" t="s">
         <v>28</v>
@@ -5211,10 +5333,10 @@
         <v>44631.713113425925</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M49" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="N49" s="7" t="s">
         <v>28</v>
@@ -5256,10 +5378,10 @@
         <v>44631.713113425925</v>
       </c>
       <c r="L50" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M50" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N50" s="7" t="s">
         <v>28</v>
@@ -5300,11 +5422,11 @@
       <c r="K51" s="6">
         <v>44631.713113425925</v>
       </c>
-      <c r="L51" s="13" t="s">
-        <v>384</v>
+      <c r="L51" s="12" t="s">
+        <v>377</v>
       </c>
       <c r="M51" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="N51" s="7" t="s">
         <v>28</v>
@@ -5348,10 +5470,10 @@
         <v>44631.713113425925</v>
       </c>
       <c r="L52" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M52" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="N52" s="7" t="s">
         <v>28</v>
@@ -5362,24 +5484,35 @@
       <c r="P52" s="7"/>
       <c r="Q52" s="7"/>
     </row>
+    <row r="53" spans="1:17">
+      <c r="A53" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="L53" s="14" t="s">
+        <v>394</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:J2"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="L1:L2"/>
     <mergeCell ref="M1:M2"/>
     <mergeCell ref="N1:N2"/>
     <mergeCell ref="O1:O2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.2" top="0.12013890000000001" bottom="0" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape"/>
@@ -5439,155 +5572,155 @@
       <c r="I1" s="9"/>
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11"/>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="13"/>
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
+    </row>
+    <row r="2" spans="1:30">
+      <c r="A2" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="V1" s="11" t="s">
+      <c r="M2" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="W1" s="11"/>
-      <c r="X1" s="11"/>
-      <c r="Y1" s="11"/>
-      <c r="Z1" s="11"/>
-      <c r="AA1" s="11"/>
-      <c r="AB1" s="11"/>
-      <c r="AC1" s="11"/>
-      <c r="AD1" s="11"/>
-    </row>
-    <row r="2" spans="1:30">
-      <c r="A2" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" s="11" t="s">
+      <c r="N2" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="O2" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="P2" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="O2" s="11" t="s">
+      <c r="S2" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="P2" s="11" t="s">
+      <c r="T2" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="U2" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="V2" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="W2" s="13"/>
+      <c r="X2" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="S2" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="T2" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="U2" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="V2" s="11" t="s">
+      <c r="AB2" s="13"/>
+      <c r="AC2" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="W2" s="11"/>
-      <c r="X2" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y2" s="11"/>
-      <c r="Z2" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA2" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="AB2" s="11"/>
-      <c r="AC2" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="AD2" s="11"/>
+      <c r="AD2" s="13"/>
     </row>
     <row r="3" spans="1:30" ht="25">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
       <c r="P3" s="1" t="s">
         <v>16</v>
       </c>
       <c r="Q3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="R3" s="11"/>
-      <c r="S3" s="11"/>
-      <c r="T3" s="11"/>
-      <c r="U3" s="11"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
+      <c r="U3" s="13"/>
       <c r="V3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="X3" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="Y3" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="X3" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="Z3" s="11"/>
+      <c r="Z3" s="13"/>
       <c r="AA3" s="1" t="s">
         <v>16</v>
       </c>
@@ -5595,10 +5728,10 @@
         <v>17</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:30">
@@ -5632,13 +5765,13 @@
         <v>44620.73710648148</v>
       </c>
       <c r="L4" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="O4" s="4" t="s">
         <v>28</v>
@@ -5646,16 +5779,16 @@
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
       <c r="R4" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="T4" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="S4" s="4" t="s">
+      <c r="U4" s="4" t="s">
         <v>139</v>
-      </c>
-      <c r="T4" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="U4" s="4" t="s">
-        <v>141</v>
       </c>
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
@@ -5698,10 +5831,10 @@
         <v>44620.73710648148</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
@@ -5710,18 +5843,18 @@
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
       <c r="T5" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="U5" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="V5" s="7"/>
       <c r="W5" s="7"/>
       <c r="X5" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="Y5" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Z5" s="7" t="s">
         <v>53</v>
@@ -5729,7 +5862,7 @@
       <c r="AA5" s="7"/>
       <c r="AB5" s="7"/>
       <c r="AC5" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AD5" s="7"/>
     </row>
@@ -5763,11 +5896,11 @@
       <c r="K6" s="6">
         <v>44620.73710648148</v>
       </c>
-      <c r="L6" s="13" t="s">
-        <v>142</v>
+      <c r="L6" s="12" t="s">
+        <v>140</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
@@ -5776,18 +5909,18 @@
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
       <c r="T6" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="U6" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="V6" s="7"/>
       <c r="W6" s="7"/>
       <c r="X6" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="Y6" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Z6" s="7" t="s">
         <v>53</v>
@@ -5795,7 +5928,7 @@
       <c r="AA6" s="7"/>
       <c r="AB6" s="7"/>
       <c r="AC6" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AD6" s="7"/>
     </row>
@@ -5832,13 +5965,13 @@
         <v>44630.666596180556</v>
       </c>
       <c r="L7" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="N7" s="7" t="s">
         <v>149</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="N7" s="7" t="s">
-        <v>151</v>
       </c>
       <c r="O7" s="7" t="s">
         <v>26</v>
@@ -5846,22 +5979,22 @@
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="S7" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="T7" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="U7" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="V7" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="S7" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="T7" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="U7" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="V7" s="7" t="s">
-        <v>154</v>
-      </c>
       <c r="W7" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="X7" s="7"/>
       <c r="Y7" s="7"/>
@@ -5871,7 +6004,7 @@
       <c r="AA7" s="7"/>
       <c r="AB7" s="7"/>
       <c r="AC7" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AD7" s="7"/>
     </row>
@@ -5908,13 +6041,13 @@
         <v>44630.666596180556</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="O8" s="7" t="s">
         <v>77</v>
@@ -5922,16 +6055,16 @@
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
       <c r="R8" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="S8" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="T8" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="S8" s="7" t="s">
+      <c r="U8" s="7" t="s">
         <v>158</v>
-      </c>
-      <c r="T8" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="U8" s="7" t="s">
-        <v>160</v>
       </c>
       <c r="V8" s="7"/>
       <c r="W8" s="7"/>
@@ -5975,11 +6108,11 @@
       <c r="K9" s="6">
         <v>44652.634575150463</v>
       </c>
-      <c r="L9" s="13" t="s">
-        <v>161</v>
+      <c r="L9" s="12" t="s">
+        <v>159</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
@@ -5991,7 +6124,7 @@
         <v>26</v>
       </c>
       <c r="U9" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="V9" s="7"/>
       <c r="W9" s="7"/>
@@ -6035,14 +6168,14 @@
       <c r="K10" s="6">
         <v>44652.652962962959</v>
       </c>
-      <c r="L10" s="13" t="s">
+      <c r="L10" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="N10" s="7" t="s">
         <v>149</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="N10" s="7" t="s">
-        <v>151</v>
       </c>
       <c r="O10" s="7" t="s">
         <v>26</v>
@@ -6050,22 +6183,22 @@
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
       <c r="R10" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="S10" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="T10" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="U10" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="V10" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="S10" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="T10" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="U10" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="V10" s="7" t="s">
-        <v>154</v>
-      </c>
       <c r="W10" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="X10" s="7"/>
       <c r="Y10" s="7"/>
@@ -6075,7 +6208,7 @@
       <c r="AA10" s="7"/>
       <c r="AB10" s="7"/>
       <c r="AC10" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AD10" s="7"/>
     </row>
@@ -6111,14 +6244,14 @@
       <c r="K11" s="6">
         <v>44652.652962962959</v>
       </c>
-      <c r="L11" s="13" t="s">
-        <v>171</v>
+      <c r="L11" s="12" t="s">
+        <v>169</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="O11" s="7" t="s">
         <v>77</v>
@@ -6128,16 +6261,16 @@
       </c>
       <c r="Q11" s="7"/>
       <c r="R11" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="S11" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="T11" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="S11" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="T11" s="7" t="s">
-        <v>159</v>
-      </c>
       <c r="U11" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="V11" s="7"/>
       <c r="W11" s="7"/>
@@ -6182,10 +6315,10 @@
         <v>44652.652962962959</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="N12" s="7"/>
       <c r="O12" s="7"/>
@@ -6197,7 +6330,7 @@
         <v>26</v>
       </c>
       <c r="U12" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="V12" s="7"/>
       <c r="W12" s="7"/>
@@ -6242,10 +6375,10 @@
         <v>44783.347083912035</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
@@ -6254,10 +6387,10 @@
       <c r="R13" s="7"/>
       <c r="S13" s="7"/>
       <c r="T13" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="U13" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="V13" s="7"/>
       <c r="W13" s="7"/>
@@ -6301,31 +6434,31 @@
       <c r="K14" s="6">
         <v>44783.347083912035</v>
       </c>
-      <c r="L14" s="13" t="s">
-        <v>385</v>
+      <c r="L14" s="12" t="s">
+        <v>378</v>
       </c>
       <c r="M14" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="O14" s="7" t="s">
         <v>166</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="O14" s="7" t="s">
-        <v>168</v>
       </c>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
       <c r="R14" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="S14" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T14" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="U14" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="V14" s="7"/>
       <c r="W14" s="7"/>
@@ -6370,10 +6503,10 @@
         <v>44783.347083912035</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="N15" s="7" t="s">
         <v>44</v>
@@ -6384,16 +6517,16 @@
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
       <c r="R15" s="7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="S15" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="T15" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="U15" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="V15" s="7"/>
       <c r="W15" s="7"/>
@@ -6407,10 +6540,10 @@
     </row>
     <row r="16" spans="1:30">
       <c r="A16" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5" t="s">
@@ -6421,7 +6554,7 @@
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>23</v>
@@ -6436,13 +6569,13 @@
         <v>44628.536451932865</v>
       </c>
       <c r="L16" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="N16" s="7" t="s">
         <v>176</v>
-      </c>
-      <c r="M16" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="N16" s="7" t="s">
-        <v>178</v>
       </c>
       <c r="O16" s="7" t="s">
         <v>26</v>
@@ -6450,14 +6583,14 @@
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
       <c r="R16" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="S16" s="7"/>
       <c r="T16" s="7" t="s">
         <v>26</v>
       </c>
       <c r="U16" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="V16" s="7"/>
       <c r="W16" s="7"/>
@@ -6471,10 +6604,10 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="5" t="s">
@@ -6485,7 +6618,7 @@
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>23</v>
@@ -6500,13 +6633,13 @@
         <v>44628.608148148145</v>
       </c>
       <c r="L17" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="N17" s="7" t="s">
         <v>176</v>
-      </c>
-      <c r="M17" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="N17" s="7" t="s">
-        <v>178</v>
       </c>
       <c r="O17" s="7" t="s">
         <v>26</v>
@@ -6514,14 +6647,14 @@
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
       <c r="R17" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="S17" s="7"/>
       <c r="T17" s="7" t="s">
         <v>26</v>
       </c>
       <c r="U17" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="V17" s="7"/>
       <c r="W17" s="7"/>
@@ -6565,14 +6698,14 @@
       <c r="K18" s="6">
         <v>44581.597650462958</v>
       </c>
-      <c r="L18" s="13" t="s">
+      <c r="L18" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="N18" s="7" t="s">
         <v>179</v>
-      </c>
-      <c r="M18" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="N18" s="7" t="s">
-        <v>181</v>
       </c>
       <c r="O18" s="7" t="s">
         <v>53</v>
@@ -6580,16 +6713,16 @@
       <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
       <c r="R18" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="S18" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T18" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="U18" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="V18" s="7"/>
       <c r="W18" s="7"/>
@@ -6633,14 +6766,14 @@
       <c r="K19" s="6">
         <v>44935.525719872683</v>
       </c>
-      <c r="L19" s="13" t="s">
-        <v>386</v>
+      <c r="L19" s="12" t="s">
+        <v>379</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="O19" s="7" t="s">
         <v>53</v>
@@ -6648,16 +6781,16 @@
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
       <c r="R19" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="S19" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="T19" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="U19" s="7" t="s">
         <v>184</v>
-      </c>
-      <c r="S19" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="T19" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="U19" s="7" t="s">
-        <v>186</v>
       </c>
       <c r="V19" s="7"/>
       <c r="W19" s="7"/>
@@ -6699,14 +6832,14 @@
       <c r="K20" s="6">
         <v>44572.604270833333</v>
       </c>
-      <c r="L20" s="13" t="s">
-        <v>376</v>
+      <c r="L20" s="12" t="s">
+        <v>370</v>
       </c>
       <c r="M20" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="O20" s="7" t="s">
         <v>53</v>
@@ -6714,16 +6847,16 @@
       <c r="P20" s="7"/>
       <c r="Q20" s="7"/>
       <c r="R20" s="7" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="S20" s="7" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="T20" s="7" t="s">
         <v>26</v>
       </c>
       <c r="U20" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="V20" s="7"/>
       <c r="W20" s="7"/>
@@ -6765,14 +6898,14 @@
       <c r="K21" s="6">
         <v>44572.604270833333</v>
       </c>
-      <c r="L21" s="13" t="s">
-        <v>376</v>
+      <c r="L21" s="12" t="s">
+        <v>370</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="O21" s="7" t="s">
         <v>53</v>
@@ -6780,16 +6913,16 @@
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
       <c r="R21" s="7" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="S21" s="7" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="T21" s="7" t="s">
         <v>26</v>
       </c>
       <c r="U21" s="7" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="V21" s="7"/>
       <c r="W21" s="7"/>
@@ -6803,23 +6936,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="V2:W2"/>
     <mergeCell ref="L1:S1"/>
     <mergeCell ref="V1:AD1"/>
     <mergeCell ref="L2:L3"/>
@@ -6830,6 +6946,23 @@
     <mergeCell ref="X2:Y2"/>
     <mergeCell ref="Z2:Z3"/>
     <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.2" top="0.12013890000000001" bottom="0" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape"/>
@@ -6887,7 +7020,7 @@
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
       <c r="L1" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M1" s="9"/>
       <c r="N1" s="9"/>
@@ -6898,7 +7031,7 @@
       <c r="S1" s="9"/>
       <c r="T1" s="9"/>
       <c r="U1" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="V1" s="9"/>
       <c r="W1" s="9"/>
@@ -6908,99 +7041,99 @@
       <c r="AA1" s="9"/>
     </row>
     <row r="2" spans="1:27">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="K2" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="O2" s="11" t="s">
+      <c r="L2" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="M2" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="N2" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="O2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11" t="s">
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="T2" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="U2" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="T2" s="11" t="s">
+      <c r="V2" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="U2" s="11" t="s">
+      <c r="W2" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="V2" s="11" t="s">
+      <c r="X2" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="W2" s="11" t="s">
+      <c r="Y2" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="X2" s="11" t="s">
+      <c r="Z2" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="Y2" s="11" t="s">
+      <c r="AA2" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="Z2" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="AA2" s="11" t="s">
-        <v>203</v>
-      </c>
     </row>
     <row r="3" spans="1:27" ht="25">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
       <c r="O3" s="1" t="s">
         <v>16</v>
       </c>
@@ -7008,38 +7141,38 @@
         <v>17</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="S3" s="11"/>
-      <c r="T3" s="11"/>
-      <c r="U3" s="11"/>
-      <c r="V3" s="11"/>
-      <c r="W3" s="11"/>
-      <c r="X3" s="11"/>
-      <c r="Y3" s="11"/>
-      <c r="Z3" s="11"/>
-      <c r="AA3" s="11"/>
+        <v>132</v>
+      </c>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
+      <c r="U3" s="13"/>
+      <c r="V3" s="13"/>
+      <c r="W3" s="13"/>
+      <c r="X3" s="13"/>
+      <c r="Y3" s="13"/>
+      <c r="Z3" s="13"/>
+      <c r="AA3" s="13"/>
     </row>
     <row r="4" spans="1:27">
       <c r="A4" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>23</v>
@@ -7054,10 +7187,10 @@
         <v>44595.715914351851</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="N4" s="4" t="s">
         <v>53</v>
@@ -7065,14 +7198,14 @@
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
       <c r="Q4" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R4" s="4"/>
       <c r="S4" s="4" t="s">
         <v>26</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="U4" s="4"/>
       <c r="V4" s="4"/>
@@ -7084,21 +7217,21 @@
     </row>
     <row r="5" spans="1:27">
       <c r="A5" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>42</v>
@@ -7113,10 +7246,10 @@
         <v>44595.727696759255</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="N5" s="7" t="s">
         <v>53</v>
@@ -7124,14 +7257,14 @@
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
       <c r="Q5" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R5" s="7"/>
       <c r="S5" s="7" t="s">
         <v>26</v>
       </c>
       <c r="T5" s="7" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="U5" s="7"/>
       <c r="V5" s="7"/>
@@ -7143,13 +7276,13 @@
     </row>
     <row r="6" spans="1:27">
       <c r="A6" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>212</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>214</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>20</v>
@@ -7159,7 +7292,7 @@
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>23</v>
@@ -7174,10 +7307,10 @@
         <v>44569.374733796292</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="N6" s="7" t="s">
         <v>53</v>
@@ -7185,12 +7318,12 @@
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
       <c r="T6" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="U6" s="7"/>
       <c r="V6" s="7"/>
@@ -7202,10 +7335,10 @@
     </row>
     <row r="7" spans="1:27">
       <c r="A7" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5" t="s">
@@ -7216,7 +7349,7 @@
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>23</v>
@@ -7231,10 +7364,10 @@
         <v>44734.482233796298</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="N7" s="7" t="s">
         <v>53</v>
@@ -7242,14 +7375,14 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R7" s="7"/>
       <c r="S7" s="7" t="s">
         <v>26</v>
       </c>
       <c r="T7" s="7" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="U7" s="7"/>
       <c r="V7" s="7"/>
@@ -7261,10 +7394,10 @@
     </row>
     <row r="8" spans="1:27">
       <c r="A8" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5" t="s">
@@ -7275,7 +7408,7 @@
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>23</v>
@@ -7290,10 +7423,10 @@
         <v>44734.482233796298</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="N8" s="7" t="s">
         <v>53</v>
@@ -7301,12 +7434,12 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R8" s="7"/>
       <c r="S8" s="7"/>
       <c r="T8" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="U8" s="7"/>
       <c r="V8" s="7"/>
@@ -7347,10 +7480,10 @@
         <v>44620.73710648148</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N9" s="7" t="s">
         <v>53</v>
@@ -7358,12 +7491,12 @@
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
       <c r="Q9" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R9" s="7"/>
       <c r="S9" s="7"/>
       <c r="T9" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="U9" s="7"/>
       <c r="V9" s="7"/>
@@ -7404,10 +7537,10 @@
         <v>44620.73710648148</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="N10" s="7" t="s">
         <v>53</v>
@@ -7415,14 +7548,14 @@
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
       <c r="Q10" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R10" s="7"/>
       <c r="S10" s="7" t="s">
         <v>26</v>
       </c>
       <c r="T10" s="7" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="U10" s="7"/>
       <c r="V10" s="7"/>
@@ -7465,10 +7598,10 @@
         <v>44630.666596180556</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="N11" s="7" t="s">
         <v>77</v>
@@ -7476,18 +7609,18 @@
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
       <c r="Q11" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R11" s="7"/>
       <c r="S11" s="7"/>
       <c r="T11" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="U11" s="7" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="V11" s="7" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="W11" s="7"/>
       <c r="X11" s="7"/>
@@ -7498,7 +7631,7 @@
         <v>25</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:27">
@@ -7534,10 +7667,10 @@
         <v>44652.652962962959</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="N12" s="7" t="s">
         <v>53</v>
@@ -7545,18 +7678,18 @@
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
       <c r="Q12" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R12" s="7"/>
       <c r="S12" s="7"/>
       <c r="T12" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="U12" s="7" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="V12" s="7" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="W12" s="7"/>
       <c r="X12" s="7"/>
@@ -7567,15 +7700,15 @@
         <v>25</v>
       </c>
       <c r="AA12" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="1:27">
       <c r="A13" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5" t="s">
@@ -7586,7 +7719,7 @@
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>23</v>
@@ -7601,10 +7734,10 @@
         <v>44665.625752314816</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="N13" s="7" t="s">
         <v>53</v>
@@ -7612,20 +7745,20 @@
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
       <c r="Q13" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R13" s="7"/>
       <c r="S13" s="7" t="s">
         <v>26</v>
       </c>
       <c r="T13" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="U13" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="V13" s="7" t="s">
         <v>234</v>
-      </c>
-      <c r="U13" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="V13" s="7" t="s">
-        <v>236</v>
       </c>
       <c r="W13" s="7"/>
       <c r="X13" s="7"/>
@@ -7633,10 +7766,10 @@
         <v>4.125</v>
       </c>
       <c r="Z13" s="7" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="AA13" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -7670,10 +7803,10 @@
         <v>44615.621944444443</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="N14" s="7" t="s">
         <v>53</v>
@@ -7681,14 +7814,14 @@
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
       <c r="Q14" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R14" s="7"/>
       <c r="S14" s="7" t="s">
         <v>26</v>
       </c>
       <c r="T14" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="U14" s="7"/>
       <c r="V14" s="7"/>
@@ -7731,10 +7864,10 @@
         <v>44650.632037037038</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="N15" s="7" t="s">
         <v>77</v>
@@ -7742,12 +7875,12 @@
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
       <c r="Q15" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R15" s="7"/>
       <c r="S15" s="7"/>
       <c r="T15" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="U15" s="7"/>
       <c r="V15" s="7"/>
@@ -7788,10 +7921,10 @@
         <v>44572.604270833333</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="N16" s="7" t="s">
         <v>53</v>
@@ -7799,14 +7932,14 @@
       <c r="O16" s="7"/>
       <c r="P16" s="7"/>
       <c r="Q16" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R16" s="7"/>
       <c r="S16" s="7" t="s">
         <v>26</v>
       </c>
       <c r="T16" s="7" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="U16" s="7"/>
       <c r="V16" s="7"/>
@@ -7847,10 +7980,10 @@
         <v>44572.604270833333</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="N17" s="7" t="s">
         <v>53</v>
@@ -7858,12 +7991,12 @@
       <c r="O17" s="7"/>
       <c r="P17" s="7"/>
       <c r="Q17" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R17" s="7"/>
       <c r="S17" s="7"/>
       <c r="T17" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="U17" s="7"/>
       <c r="V17" s="7"/>
@@ -7904,10 +8037,10 @@
         <v>44631.713113425925</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="N18" s="7" t="s">
         <v>53</v>
@@ -7915,12 +8048,12 @@
       <c r="O18" s="7"/>
       <c r="P18" s="7"/>
       <c r="Q18" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R18" s="7"/>
       <c r="S18" s="7"/>
       <c r="T18" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="U18" s="7"/>
       <c r="V18" s="7"/>
@@ -7932,16 +8065,12 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="Z2:Z3"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="S2:S3"/>
@@ -7951,12 +8080,16 @@
     <mergeCell ref="L2:L3"/>
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
-    <mergeCell ref="AA2:AA3"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="X2:X3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.2" top="0.12013890000000001" bottom="0" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape"/>
@@ -8005,105 +8138,105 @@
       <c r="I1" s="9"/>
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="M2" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11"/>
-    </row>
-    <row r="2" spans="1:19">
-      <c r="A2" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" s="11" t="s">
+      <c r="N2" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="O2" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="P2" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="Q2" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="O2" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="P2" s="11" t="s">
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
+    </row>
+    <row r="3" spans="1:19" ht="25">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="Q2" s="11" t="s">
+      <c r="R3" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-    </row>
-    <row r="3" spans="1:19" ht="25">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
@@ -8114,7 +8247,7 @@
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>23</v>
@@ -8129,32 +8262,32 @@
         <v>44734.482233796298</v>
       </c>
       <c r="L4" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="O4" s="4" t="s">
         <v>256</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>258</v>
       </c>
       <c r="P4" s="4" t="s">
         <v>26</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5" t="s">
@@ -8165,7 +8298,7 @@
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>23</v>
@@ -8180,22 +8313,22 @@
         <v>44734.482233796298</v>
       </c>
       <c r="L5" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="N5" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="M5" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>257</v>
-      </c>
       <c r="O5" s="7" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="P5" s="7" t="s">
         <v>26</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
@@ -8230,23 +8363,23 @@
       <c r="K6" s="6">
         <v>44635.468206018515</v>
       </c>
-      <c r="L6" s="13" t="s">
-        <v>387</v>
+      <c r="L6" s="12" t="s">
+        <v>380</v>
       </c>
       <c r="M6" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="O6" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="N6" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="O6" s="7" t="s">
-        <v>264</v>
-      </c>
       <c r="P6" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
@@ -8281,23 +8414,23 @@
       <c r="K7" s="6">
         <v>44635.468206018515</v>
       </c>
-      <c r="L7" s="13" t="s">
-        <v>388</v>
+      <c r="L7" s="12" t="s">
+        <v>381</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P7" s="7" t="s">
         <v>26</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="R7" s="7"/>
       <c r="S7" s="7"/>
@@ -8336,17 +8469,17 @@
       </c>
       <c r="L8" s="7"/>
       <c r="M8" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="N8" s="7"/>
       <c r="O8" s="7" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="R8" s="7"/>
       <c r="S8" s="7"/>
@@ -8385,19 +8518,19 @@
       </c>
       <c r="L9" s="7"/>
       <c r="M9" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="O9" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="N9" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="O9" s="7" t="s">
-        <v>270</v>
-      </c>
       <c r="P9" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="R9" s="7"/>
       <c r="S9" s="7"/>
@@ -8436,19 +8569,19 @@
       </c>
       <c r="L10" s="7"/>
       <c r="M10" s="7" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
@@ -8487,19 +8620,19 @@
       </c>
       <c r="L11" s="7"/>
       <c r="M11" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="R11" s="7"/>
       <c r="S11" s="7"/>
@@ -8538,19 +8671,19 @@
       </c>
       <c r="L12" s="7"/>
       <c r="M12" s="7" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="P12" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="R12" s="7"/>
       <c r="S12" s="7"/>
@@ -8588,32 +8721,32 @@
         <v>44783.347083912035</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="R13" s="7"/>
       <c r="S13" s="7"/>
     </row>
     <row r="14" spans="1:19">
       <c r="A14" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5" t="s">
@@ -8624,7 +8757,7 @@
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>23</v>
@@ -8639,32 +8772,32 @@
         <v>44665.625752314816</v>
       </c>
       <c r="L14" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="N14" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="M14" s="7" t="s">
+      <c r="O14" s="7" t="s">
         <v>274</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="O14" s="7" t="s">
-        <v>276</v>
       </c>
       <c r="P14" s="7" t="s">
         <v>26</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="R14" s="7"/>
       <c r="S14" s="7"/>
     </row>
     <row r="15" spans="1:19">
       <c r="A15" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5" t="s">
@@ -8675,7 +8808,7 @@
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>23</v>
@@ -8690,32 +8823,32 @@
         <v>44665.625752314816</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="R15" s="7"/>
       <c r="S15" s="7"/>
     </row>
     <row r="16" spans="1:19">
       <c r="A16" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5" t="s">
@@ -8726,7 +8859,7 @@
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>23</v>
@@ -8742,29 +8875,29 @@
       </c>
       <c r="L16" s="7"/>
       <c r="M16" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="O16" s="7" t="s">
         <v>279</v>
-      </c>
-      <c r="N16" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="O16" s="7" t="s">
-        <v>281</v>
       </c>
       <c r="P16" s="7" t="s">
         <v>26</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="R16" s="7"/>
       <c r="S16" s="7"/>
     </row>
     <row r="17" spans="1:19">
       <c r="A17" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="5" t="s">
@@ -8775,7 +8908,7 @@
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>23</v>
@@ -8790,30 +8923,30 @@
         <v>44665.625752314816</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="N17" s="7"/>
       <c r="O17" s="7"/>
       <c r="P17" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="R17" s="7" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="S17" s="7"/>
     </row>
     <row r="18" spans="1:19">
       <c r="A18" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5" t="s">
@@ -8824,7 +8957,7 @@
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>23</v>
@@ -8839,30 +8972,30 @@
         <v>44628.536451932865</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="N18" s="7"/>
       <c r="O18" s="7" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="P18" s="7" t="s">
         <v>26</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="R18" s="7"/>
       <c r="S18" s="7"/>
     </row>
     <row r="19" spans="1:19">
       <c r="A19" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="5" t="s">
@@ -8873,7 +9006,7 @@
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>23</v>
@@ -8888,20 +9021,20 @@
         <v>44628.608148148145</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="N19" s="7"/>
       <c r="O19" s="7" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="P19" s="7" t="s">
         <v>26</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="R19" s="7"/>
       <c r="S19" s="7"/>
@@ -8937,22 +9070,22 @@
         <v>44615.621944444443</v>
       </c>
       <c r="L20" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="N20" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="M20" s="7" t="s">
+      <c r="O20" s="7" t="s">
         <v>291</v>
-      </c>
-      <c r="N20" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="O20" s="7" t="s">
-        <v>293</v>
       </c>
       <c r="P20" s="7" t="s">
         <v>26</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="R20" s="7"/>
       <c r="S20" s="7"/>
@@ -8990,22 +9123,22 @@
         <v>44581.597650462958</v>
       </c>
       <c r="L21" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="N21" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="M21" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="N21" s="7" t="s">
-        <v>181</v>
-      </c>
       <c r="O21" s="7" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R21" s="7"/>
       <c r="S21" s="7"/>
@@ -9042,36 +9175,36 @@
       <c r="K22" s="6">
         <v>44587.558275462958</v>
       </c>
-      <c r="L22" s="13" t="s">
-        <v>386</v>
+      <c r="L22" s="12" t="s">
+        <v>379</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="R22" s="7"/>
       <c r="S22" s="7"/>
     </row>
     <row r="23" spans="1:19">
       <c r="A23" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>297</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>299</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>20</v>
@@ -9081,7 +9214,7 @@
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>23</v>
@@ -9096,35 +9229,35 @@
         <v>44621.497152777774</v>
       </c>
       <c r="L23" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="N23" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="M23" s="7" t="s">
+      <c r="O23" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="N23" s="7" t="s">
+      <c r="P23" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q23" s="7" t="s">
         <v>303</v>
-      </c>
-      <c r="O23" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="P23" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q23" s="7" t="s">
-        <v>305</v>
       </c>
       <c r="R23" s="7"/>
       <c r="S23" s="7"/>
     </row>
     <row r="24" spans="1:19">
       <c r="A24" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>297</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>299</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>20</v>
@@ -9134,7 +9267,7 @@
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>23</v>
@@ -9148,36 +9281,36 @@
       <c r="K24" s="6">
         <v>44621.497152777774</v>
       </c>
-      <c r="L24" s="13" t="s">
-        <v>389</v>
+      <c r="L24" s="12" t="s">
+        <v>382</v>
       </c>
       <c r="M24" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="O24" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="N24" s="7" t="s">
+      <c r="P24" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="O24" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="P24" s="7" t="s">
-        <v>309</v>
-      </c>
       <c r="Q24" s="7" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="R24" s="7"/>
       <c r="S24" s="7"/>
     </row>
     <row r="25" spans="1:19">
       <c r="A25" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>297</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>299</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>20</v>
@@ -9187,7 +9320,7 @@
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>23</v>
@@ -9201,36 +9334,36 @@
       <c r="K25" s="6">
         <v>44621.497152777774</v>
       </c>
-      <c r="L25" s="13" t="s">
-        <v>390</v>
+      <c r="L25" s="12" t="s">
+        <v>383</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="P25" s="7" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="Q25" s="7" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="R25" s="7"/>
       <c r="S25" s="7"/>
     </row>
     <row r="26" spans="1:19">
       <c r="A26" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>297</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>299</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>20</v>
@@ -9240,7 +9373,7 @@
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>23</v>
@@ -9254,36 +9387,36 @@
       <c r="K26" s="6">
         <v>44621.497152777774</v>
       </c>
-      <c r="L26" s="13" t="s">
-        <v>391</v>
+      <c r="L26" s="12" t="s">
+        <v>384</v>
       </c>
       <c r="M26" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="N26" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="O26" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="N26" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="O26" s="7" t="s">
-        <v>304</v>
-      </c>
       <c r="P26" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="Q26" s="7" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="R26" s="7"/>
       <c r="S26" s="7"/>
     </row>
     <row r="27" spans="1:19">
       <c r="A27" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>297</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>299</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>20</v>
@@ -9293,7 +9426,7 @@
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>23</v>
@@ -9308,20 +9441,20 @@
         <v>44621.497152777774</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="N27" s="7"/>
       <c r="O27" s="7" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="P27" s="7" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="Q27" s="7" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="R27" s="7"/>
       <c r="S27" s="7"/>
@@ -9356,23 +9489,23 @@
       <c r="K28" s="6">
         <v>44631.713113425925</v>
       </c>
-      <c r="L28" s="13" t="s">
-        <v>392</v>
+      <c r="L28" s="12" t="s">
+        <v>385</v>
       </c>
       <c r="M28" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="N28" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="O28" s="7" t="s">
         <v>315</v>
-      </c>
-      <c r="N28" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="O28" s="7" t="s">
-        <v>317</v>
       </c>
       <c r="P28" s="7" t="s">
         <v>26</v>
       </c>
       <c r="Q28" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="R28" s="7"/>
       <c r="S28" s="7"/>
@@ -9407,39 +9540,29 @@
       <c r="K29" s="6">
         <v>44631.713113425925</v>
       </c>
-      <c r="L29" s="13" t="s">
-        <v>393</v>
+      <c r="L29" s="12" t="s">
+        <v>386</v>
       </c>
       <c r="M29" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="N29" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="O29" s="7" t="s">
         <v>318</v>
-      </c>
-      <c r="N29" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="O29" s="7" t="s">
-        <v>320</v>
       </c>
       <c r="P29" s="7" t="s">
         <v>26</v>
       </c>
       <c r="Q29" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="R29" s="7"/>
       <c r="S29" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="L1:S1"/>
     <mergeCell ref="L2:L3"/>
@@ -9448,6 +9571,16 @@
     <mergeCell ref="O2:O3"/>
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.2" top="0.12013890000000001" bottom="0" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape"/>
@@ -9518,25 +9651,25 @@
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -9570,14 +9703,14 @@
         <v>44620.73710648148</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="N2" s="4"/>
       <c r="O2" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="P2" s="10">
         <v>44427</v>
@@ -9586,7 +9719,7 @@
         <v>200</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -9620,14 +9753,14 @@
         <v>44631.713113425925</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="N3" s="7"/>
       <c r="O3" s="7" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="P3" s="8">
         <v>44291</v>
@@ -9636,7 +9769,7 @@
         <v>100</v>
       </c>
       <c r="R3" s="7" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -9670,14 +9803,14 @@
         <v>44631.713113425925</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="N4" s="7"/>
       <c r="O4" s="7" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="P4" s="8">
         <v>44447</v>
@@ -9686,7 +9819,7 @@
         <v>100</v>
       </c>
       <c r="R4" s="7" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -9720,14 +9853,14 @@
         <v>44631.713113425925</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="N5" s="7"/>
       <c r="O5" s="7" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="P5" s="8">
         <v>44477</v>
@@ -9736,7 +9869,7 @@
         <v>50</v>
       </c>
       <c r="R5" s="7" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -9770,14 +9903,14 @@
         <v>44631.713113425925</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="N6" s="7"/>
       <c r="O6" s="7" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="P6" s="8">
         <v>44305</v>
@@ -9786,7 +9919,7 @@
         <v>50</v>
       </c>
       <c r="R6" s="7" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -9828,98 +9961,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="M1" s="11" t="s">
+      <c r="L1" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="M1" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="N1" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="O1" s="13" t="s">
         <v>339</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="P1" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q1" s="13" t="s">
         <v>340</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="R1" s="13"/>
+      <c r="S1" s="13" t="s">
         <v>341</v>
       </c>
-      <c r="P1" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="Q1" s="11" t="s">
+      <c r="T1" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11" t="s">
+      <c r="U1" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="T1" s="11" t="s">
+      <c r="V1" s="13" t="s">
         <v>344</v>
       </c>
-      <c r="U1" s="11" t="s">
+    </row>
+    <row r="2" spans="1:22">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="V1" s="11" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="1" t="s">
-        <v>347</v>
-      </c>
       <c r="R2" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="S2" s="11"/>
-      <c r="T2" s="11"/>
-      <c r="U2" s="11"/>
-      <c r="V2" s="11"/>
+        <v>345</v>
+      </c>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="13"/>
+      <c r="V2" s="13"/>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="2" t="s">
@@ -9954,13 +10087,13 @@
         <v>44630.666596180556</v>
       </c>
       <c r="L3" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="N3" s="4" t="s">
         <v>348</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>350</v>
       </c>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
@@ -9970,10 +10103,10 @@
         <v>9506.7199999999993</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="V3" s="4"/>
     </row>
@@ -10010,13 +10143,13 @@
         <v>44652.652962962959</v>
       </c>
       <c r="L4" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="N4" s="7" t="s">
         <v>348</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>350</v>
       </c>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
@@ -10026,25 +10159,15 @@
         <v>9506.7199999999993</v>
       </c>
       <c r="T4" s="7" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="U4" s="7" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="V4" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:J2"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="V1:V2"/>
     <mergeCell ref="U1:U2"/>
@@ -10056,6 +10179,16 @@
     <mergeCell ref="P1:P2"/>
     <mergeCell ref="S1:S2"/>
     <mergeCell ref="T1:T2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.2" top="0.12013890000000001" bottom="0" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape"/>

--- a/data/form_700/sonoma_2021.xlsx
+++ b/data/form_700/sonoma_2021.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/david/local_csci/csc131_project/data/form_700/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDFF8A36-F06E-EC4B-A50A-FABB6D001795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F3840D8-13D8-3142-AD82-BE1DDCC303A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="29020" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="660" yWindow="3520" windowWidth="29020" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Schedule A1" sheetId="2" r:id="rId1"/>
@@ -1175,7 +1175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="394">
   <si>
     <t>Last Name</t>
   </si>
@@ -2443,9 +2443,6 @@
     <t>Portfolia Consumer Fund</t>
   </si>
   <si>
-    <t>KEYS#Keysight Technologies Inc.</t>
-  </si>
-  <si>
     <t>ARC Healthcare</t>
   </si>
   <si>
@@ -2560,13 +2557,13 @@
     <t>Walmart#WMT</t>
   </si>
   <si>
-    <t>Walt Disney</t>
-  </si>
-  <si>
     <t>HPQ#Hewlett-Packard#Hewlett Packard</t>
   </si>
   <si>
-    <t>landpaths</t>
+    <t>KEYS#Keysight Technologies</t>
+  </si>
+  <si>
+    <t>Landpaths</t>
   </si>
 </sst>
 </file>
@@ -2796,10 +2793,10 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3133,72 +3130,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="M1" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="N1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="O1" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="P1" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="13"/>
+      <c r="Q1" s="14"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
       <c r="P2" s="1" t="s">
         <v>16</v>
       </c>
@@ -3237,7 +3234,7 @@
         <v>44620.73710648148</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="M3" s="4" t="s">
         <v>25</v>
@@ -3282,7 +3279,7 @@
         <v>44620.73710648148</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="M4" s="7" t="s">
         <v>25</v>
@@ -3327,7 +3324,7 @@
         <v>44620.73710648148</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="M5" s="7" t="s">
         <v>25</v>
@@ -3372,7 +3369,7 @@
         <v>44620.73710648148</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>27</v>
@@ -3417,7 +3414,7 @@
         <v>44620.73710648148</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="M7" s="7" t="s">
         <v>25</v>
@@ -3507,7 +3504,7 @@
         <v>44620.73710648148</v>
       </c>
       <c r="L9" s="12" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="M9" s="7" t="s">
         <v>25</v>
@@ -3552,7 +3549,7 @@
         <v>44620.73710648148</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="M10" s="7" t="s">
         <v>31</v>
@@ -3597,7 +3594,7 @@
         <v>44620.73710648148</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="M11" s="7" t="s">
         <v>30</v>
@@ -3642,7 +3639,7 @@
         <v>44635.468206018515</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>392</v>
+        <v>105</v>
       </c>
       <c r="M12" s="7" t="s">
         <v>37</v>
@@ -3829,8 +3826,8 @@
       <c r="K16" s="6">
         <v>44628.593032407407</v>
       </c>
-      <c r="L16" s="12" t="s">
-        <v>353</v>
+      <c r="L16" s="7" t="s">
+        <v>392</v>
       </c>
       <c r="M16" s="7" t="s">
         <v>52</v>
@@ -3877,7 +3874,7 @@
         <v>44628.593032407407</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="M17" s="7" t="s">
         <v>52</v>
@@ -3924,7 +3921,7 @@
         <v>44628.593032407407</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="M18" s="7" t="s">
         <v>52</v>
@@ -3971,7 +3968,7 @@
         <v>44628.593032407407</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="M19" s="7" t="s">
         <v>52</v>
@@ -4018,7 +4015,7 @@
         <v>44628.593032407407</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="M20" s="7" t="s">
         <v>52</v>
@@ -4065,7 +4062,7 @@
         <v>44628.593032407407</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="M21" s="7" t="s">
         <v>52</v>
@@ -4110,7 +4107,7 @@
         <v>44615.621944444443</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="M22" s="7" t="s">
         <v>57</v>
@@ -4155,7 +4152,7 @@
         <v>44615.621944444443</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="M23" s="7" t="s">
         <v>58</v>
@@ -4245,7 +4242,7 @@
         <v>44615.621944444443</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="M25" s="7" t="s">
         <v>61</v>
@@ -4290,7 +4287,7 @@
         <v>44615.621944444443</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="M26" s="7" t="s">
         <v>62</v>
@@ -4335,7 +4332,7 @@
         <v>44615.621944444443</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="M27" s="7" t="s">
         <v>62</v>
@@ -4476,7 +4473,7 @@
         <v>44587.558275462958</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="M30" s="7" t="s">
         <v>75</v>
@@ -4523,7 +4520,7 @@
         <v>44587.558275462958</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="M31" s="7" t="s">
         <v>76</v>
@@ -4568,7 +4565,7 @@
         <v>44572.604270833333</v>
       </c>
       <c r="L32" s="12" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M32" s="7" t="s">
         <v>82</v>
@@ -4613,7 +4610,7 @@
         <v>44631.713113425925</v>
       </c>
       <c r="L33" s="12" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="M33" s="7" t="s">
         <v>88</v>
@@ -4658,7 +4655,7 @@
         <v>44631.713113425925</v>
       </c>
       <c r="L34" s="12" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="M34" s="7" t="s">
         <v>44</v>
@@ -4703,7 +4700,7 @@
         <v>44631.713113425925</v>
       </c>
       <c r="L35" s="12" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="M35" s="7" t="s">
         <v>89</v>
@@ -4928,7 +4925,7 @@
         <v>44631.713113425925</v>
       </c>
       <c r="L40" s="7" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="M40" s="7" t="s">
         <v>44</v>
@@ -4973,7 +4970,7 @@
         <v>44631.713113425925</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="M41" s="7" t="s">
         <v>97</v>
@@ -5063,7 +5060,7 @@
         <v>44631.713113425925</v>
       </c>
       <c r="L43" s="12" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="M43" s="7" t="s">
         <v>44</v>
@@ -5108,7 +5105,7 @@
         <v>44631.713113425925</v>
       </c>
       <c r="L44" s="12" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="M44" s="7" t="s">
         <v>99</v>
@@ -5243,7 +5240,7 @@
         <v>44631.713113425925</v>
       </c>
       <c r="L47" s="7" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="M47" s="7" t="s">
         <v>103</v>
@@ -5288,7 +5285,7 @@
         <v>44631.713113425925</v>
       </c>
       <c r="L48" s="12" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="M48" s="7" t="s">
         <v>104</v>
@@ -5423,7 +5420,7 @@
         <v>44631.713113425925</v>
       </c>
       <c r="L51" s="12" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M51" s="7" t="s">
         <v>109</v>
@@ -5491,28 +5488,28 @@
       <c r="B53" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="L53" s="14" t="s">
-        <v>394</v>
+      <c r="L53" s="13" t="s">
+        <v>393</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="L1:L2"/>
     <mergeCell ref="M1:M2"/>
     <mergeCell ref="N1:N2"/>
     <mergeCell ref="O1:O2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.2" top="0.12013890000000001" bottom="0" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape"/>
@@ -5572,142 +5569,142 @@
       <c r="I1" s="9"/>
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
       <c r="T1" s="1" t="s">
         <v>113</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="V1" s="13" t="s">
+      <c r="V1" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
-      <c r="Y1" s="13"/>
-      <c r="Z1" s="13"/>
-      <c r="AA1" s="13"/>
-      <c r="AB1" s="13"/>
-      <c r="AC1" s="13"/>
-      <c r="AD1" s="13"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
+      <c r="Y1" s="14"/>
+      <c r="Z1" s="14"/>
+      <c r="AA1" s="14"/>
+      <c r="AB1" s="14"/>
+      <c r="AC1" s="14"/>
+      <c r="AD1" s="14"/>
     </row>
     <row r="2" spans="1:30">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="13" t="s">
+      <c r="L2" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="M2" s="13" t="s">
+      <c r="M2" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="N2" s="13" t="s">
+      <c r="N2" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="O2" s="13" t="s">
+      <c r="O2" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="P2" s="13" t="s">
+      <c r="P2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13" t="s">
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="S2" s="13" t="s">
+      <c r="S2" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="T2" s="13" t="s">
+      <c r="T2" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="U2" s="13" t="s">
+      <c r="U2" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="V2" s="13" t="s">
+      <c r="V2" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="W2" s="13"/>
-      <c r="X2" s="13" t="s">
+      <c r="W2" s="14"/>
+      <c r="X2" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="Y2" s="13"/>
-      <c r="Z2" s="13" t="s">
+      <c r="Y2" s="14"/>
+      <c r="Z2" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="AA2" s="13" t="s">
+      <c r="AA2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="AB2" s="13"/>
-      <c r="AC2" s="13" t="s">
+      <c r="AB2" s="14"/>
+      <c r="AC2" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="AD2" s="13"/>
+      <c r="AD2" s="14"/>
     </row>
     <row r="3" spans="1:30" ht="25">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
       <c r="P3" s="1" t="s">
         <v>16</v>
       </c>
       <c r="Q3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
-      <c r="U3" s="13"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="14"/>
       <c r="V3" s="1" t="s">
         <v>127</v>
       </c>
@@ -5720,7 +5717,7 @@
       <c r="Y3" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="Z3" s="13"/>
+      <c r="Z3" s="14"/>
       <c r="AA3" s="1" t="s">
         <v>16</v>
       </c>
@@ -6435,7 +6432,7 @@
         <v>44783.347083912035</v>
       </c>
       <c r="L14" s="12" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="M14" s="7" t="s">
         <v>164</v>
@@ -6767,7 +6764,7 @@
         <v>44935.525719872683</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="M19" s="7" t="s">
         <v>180</v>
@@ -6833,7 +6830,7 @@
         <v>44572.604270833333</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M20" s="7" t="s">
         <v>185</v>
@@ -6899,7 +6896,7 @@
         <v>44572.604270833333</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M21" s="7" t="s">
         <v>185</v>
@@ -6936,6 +6933,23 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="V2:W2"/>
     <mergeCell ref="L1:S1"/>
     <mergeCell ref="V1:AD1"/>
     <mergeCell ref="L2:L3"/>
@@ -6946,23 +6960,6 @@
     <mergeCell ref="X2:Y2"/>
     <mergeCell ref="Z2:Z3"/>
     <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="V2:W2"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.2" top="0.12013890000000001" bottom="0" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape"/>
@@ -7041,99 +7038,99 @@
       <c r="AA1" s="9"/>
     </row>
     <row r="2" spans="1:27">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="13" t="s">
+      <c r="L2" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="M2" s="13" t="s">
+      <c r="M2" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="N2" s="13" t="s">
+      <c r="N2" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="O2" s="13" t="s">
+      <c r="O2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13" t="s">
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="R2" s="13"/>
-      <c r="S2" s="13" t="s">
+      <c r="R2" s="14"/>
+      <c r="S2" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="T2" s="13" t="s">
+      <c r="T2" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="U2" s="13" t="s">
+      <c r="U2" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="V2" s="13" t="s">
+      <c r="V2" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="W2" s="13" t="s">
+      <c r="W2" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="X2" s="13" t="s">
+      <c r="X2" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="Y2" s="13" t="s">
+      <c r="Y2" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="Z2" s="13" t="s">
+      <c r="Z2" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="AA2" s="13" t="s">
+      <c r="AA2" s="14" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="25">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
       <c r="O3" s="1" t="s">
         <v>16</v>
       </c>
@@ -7146,15 +7143,15 @@
       <c r="R3" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
-      <c r="U3" s="13"/>
-      <c r="V3" s="13"/>
-      <c r="W3" s="13"/>
-      <c r="X3" s="13"/>
-      <c r="Y3" s="13"/>
-      <c r="Z3" s="13"/>
-      <c r="AA3" s="13"/>
+      <c r="S3" s="14"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="14"/>
+      <c r="V3" s="14"/>
+      <c r="W3" s="14"/>
+      <c r="X3" s="14"/>
+      <c r="Y3" s="14"/>
+      <c r="Z3" s="14"/>
+      <c r="AA3" s="14"/>
     </row>
     <row r="4" spans="1:27">
       <c r="A4" s="2" t="s">
@@ -8065,12 +8062,16 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="AA2:AA3"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="X2:X3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="S2:S3"/>
@@ -8080,16 +8081,12 @@
     <mergeCell ref="L2:L3"/>
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="Z2:Z3"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.2" top="0.12013890000000001" bottom="0" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape"/>
@@ -8138,89 +8135,89 @@
       <c r="I1" s="9"/>
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="13" t="s">
+      <c r="L2" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="M2" s="13" t="s">
+      <c r="M2" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="N2" s="13" t="s">
+      <c r="N2" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="O2" s="13" t="s">
+      <c r="O2" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="P2" s="13" t="s">
+      <c r="P2" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="Q2" s="13" t="s">
+      <c r="Q2" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="R2" s="13"/>
-      <c r="S2" s="13"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
     </row>
     <row r="3" spans="1:19" ht="25">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
       <c r="Q3" s="1" t="s">
         <v>250</v>
       </c>
@@ -8364,7 +8361,7 @@
         <v>44635.468206018515</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>260</v>
@@ -8415,7 +8412,7 @@
         <v>44635.468206018515</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="M7" s="7" t="s">
         <v>260</v>
@@ -9176,7 +9173,7 @@
         <v>44587.558275462958</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="M22" s="7" t="s">
         <v>180</v>
@@ -9282,7 +9279,7 @@
         <v>44621.497152777774</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="M24" s="7" t="s">
         <v>304</v>
@@ -9335,7 +9332,7 @@
         <v>44621.497152777774</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="M25" s="7" t="s">
         <v>308</v>
@@ -9388,7 +9385,7 @@
         <v>44621.497152777774</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="M26" s="7" t="s">
         <v>300</v>
@@ -9490,7 +9487,7 @@
         <v>44631.713113425925</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="M28" s="7" t="s">
         <v>313</v>
@@ -9541,7 +9538,7 @@
         <v>44631.713113425925</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="M29" s="7" t="s">
         <v>316</v>
@@ -9563,6 +9560,16 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="L1:S1"/>
     <mergeCell ref="L2:L3"/>
@@ -9571,16 +9578,6 @@
     <mergeCell ref="O2:O3"/>
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.2" top="0.12013890000000001" bottom="0" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape"/>
@@ -9961,98 +9958,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="M1" s="14" t="s">
         <v>337</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="N1" s="14" t="s">
         <v>338</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="O1" s="14" t="s">
         <v>339</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="P1" s="14" t="s">
         <v>321</v>
       </c>
-      <c r="Q1" s="13" t="s">
+      <c r="Q1" s="14" t="s">
         <v>340</v>
       </c>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13" t="s">
+      <c r="R1" s="14"/>
+      <c r="S1" s="14" t="s">
         <v>341</v>
       </c>
-      <c r="T1" s="13" t="s">
+      <c r="T1" s="14" t="s">
         <v>342</v>
       </c>
-      <c r="U1" s="13" t="s">
+      <c r="U1" s="14" t="s">
         <v>343</v>
       </c>
-      <c r="V1" s="13" t="s">
+      <c r="V1" s="14" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="2" spans="1:22">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
       <c r="Q2" s="1" t="s">
         <v>345</v>
       </c>
       <c r="R2" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="S2" s="13"/>
-      <c r="T2" s="13"/>
-      <c r="U2" s="13"/>
-      <c r="V2" s="13"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="14"/>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="2" t="s">
@@ -10168,6 +10165,16 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="V1:V2"/>
     <mergeCell ref="U1:U2"/>
@@ -10179,16 +10186,6 @@
     <mergeCell ref="P1:P2"/>
     <mergeCell ref="S1:S2"/>
     <mergeCell ref="T1:T2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.2" top="0.12013890000000001" bottom="0" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape"/>
